--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_maule.xlsx
@@ -72,12 +72,12 @@
     <t xml:space="preserve">San Clemente</t>
   </si>
   <si>
+    <t xml:space="preserve">Villa Alegre</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cauquenes</t>
   </si>
   <si>
-    <t xml:space="preserve">Villa Alegre</t>
-  </si>
-  <si>
     <t xml:space="preserve">Parral</t>
   </si>
   <si>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:27</t>
+    <t xml:space="preserve">2026-09-09 23:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -766,7 +766,7 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>7201</v>
+        <v>7407</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2021</v>
@@ -783,7 +783,7 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>7407</v>
+        <v>7201</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2021</v>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:24</t>
+    <t xml:space="preserve">2026-09-17 14:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_maule.xlsx
@@ -60,33 +60,33 @@
     <t xml:space="preserve">Teno</t>
   </si>
   <si>
+    <t xml:space="preserve">Romeral</t>
+  </si>
+  <si>
     <t xml:space="preserve">Retiro</t>
   </si>
   <si>
-    <t xml:space="preserve">Romeral</t>
-  </si>
-  <si>
     <t xml:space="preserve">Yerbas Buenas</t>
   </si>
   <si>
     <t xml:space="preserve">San Clemente</t>
   </si>
   <si>
+    <t xml:space="preserve">Cauquenes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Villa Alegre</t>
   </si>
   <si>
-    <t xml:space="preserve">Cauquenes</t>
-  </si>
-  <si>
     <t xml:space="preserve">Parral</t>
   </si>
   <si>
+    <t xml:space="preserve">Curicó</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Javier</t>
   </si>
   <si>
-    <t xml:space="preserve">Curicó</t>
-  </si>
-  <si>
     <t xml:space="preserve">Colbún</t>
   </si>
   <si>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:19</t>
+    <t xml:space="preserve">2026-09-23 12:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -698,7 +698,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>7405</v>
+        <v>7306</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2021</v>
@@ -715,7 +715,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>7306</v>
+        <v>7405</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2021</v>
@@ -766,7 +766,7 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>7407</v>
+        <v>7201</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2021</v>
@@ -783,7 +783,7 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>7201</v>
+        <v>7407</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2021</v>
@@ -817,7 +817,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>7406</v>
+        <v>7301</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2021</v>
@@ -834,7 +834,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>7301</v>
+        <v>7406</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2021</v>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_maule.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:47</t>
+    <t xml:space="preserve">2026-10-01 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre la mediana nacional (%)</t>
+    <t xml:space="preserve">% bajo 50% de la mediana</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -163,9 +163,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre mediana</t>
   </si>
 </sst>
 </file>
@@ -1141,7 +1138,7 @@
         <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:06</t>
+    <t xml:space="preserve">2026-10-02 11:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:20</t>
+    <t xml:space="preserve">2026-10-02 15:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:06</t>
+    <t xml:space="preserve">2026-10-05 12:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
